--- a/artfynd/A 30176-2024 artfynd.xlsx
+++ b/artfynd/A 30176-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73919881</v>
+        <v>73919878</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470335.9270473992</v>
+        <v>470286</v>
       </c>
       <c r="R2" t="n">
-        <v>6728776.138039314</v>
+        <v>6728752</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73919879</v>
+        <v>73919882</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470335.9270473992</v>
+        <v>470407</v>
       </c>
       <c r="R3" t="n">
-        <v>6728776.138039314</v>
+        <v>6728820</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73919882</v>
+        <v>73919871</v>
       </c>
       <c r="B4" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470406.9300431631</v>
+        <v>470139</v>
       </c>
       <c r="R4" t="n">
-        <v>6728820.120126657</v>
+        <v>6728514</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73919878</v>
+        <v>73919880</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470286.181370063</v>
+        <v>470336</v>
       </c>
       <c r="R5" t="n">
-        <v>6728752.061286475</v>
+        <v>6728776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73919880</v>
+        <v>73919896</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470335.9270473992</v>
+        <v>470162</v>
       </c>
       <c r="R6" t="n">
-        <v>6728776.138039314</v>
+        <v>6728903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73919873</v>
+        <v>73919870</v>
       </c>
       <c r="B7" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470403.1944814678</v>
+        <v>470139</v>
       </c>
       <c r="R7" t="n">
-        <v>6728605.139829178</v>
+        <v>6728514</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73919876</v>
+        <v>73919879</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470409.224646021</v>
+        <v>470336</v>
       </c>
       <c r="R8" t="n">
-        <v>6728681.986200528</v>
+        <v>6728776</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73919872</v>
+        <v>73919895</v>
       </c>
       <c r="B9" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470138.9923281256</v>
+        <v>470162</v>
       </c>
       <c r="R9" t="n">
-        <v>6728513.777862485</v>
+        <v>6728903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73919893</v>
+        <v>73919874</v>
       </c>
       <c r="B10" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470295.761082568</v>
+        <v>470462</v>
       </c>
       <c r="R10" t="n">
-        <v>6728901.848360936</v>
+        <v>6728582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73919874</v>
+        <v>73919876</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470461.8746497087</v>
+        <v>470409</v>
       </c>
       <c r="R11" t="n">
-        <v>6728582.125887427</v>
+        <v>6728682</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73919871</v>
+        <v>73919877</v>
       </c>
       <c r="B12" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470138.9923281256</v>
+        <v>470419</v>
       </c>
       <c r="R12" t="n">
-        <v>6728513.777862485</v>
+        <v>6728694</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,14 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>m7asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73919877</v>
+        <v>73919872</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470419.1363194168</v>
+        <v>470139</v>
       </c>
       <c r="R13" t="n">
-        <v>6728694.148919889</v>
+        <v>6728514</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,24 +1815,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>m7asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,15 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73919894</v>
+        <v>73919873</v>
       </c>
       <c r="B14" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470195.7994911244</v>
+        <v>470403</v>
       </c>
       <c r="R14" t="n">
-        <v>6728914.921120371</v>
+        <v>6728605</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,19 +1912,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,37 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>73919870</v>
+        <v>73919881</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470138.9923281256</v>
+        <v>470336</v>
       </c>
       <c r="R15" t="n">
-        <v>6728513.777862485</v>
+        <v>6728776</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,19 +2009,9 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,6 +2035,200 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>73919893</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dalarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>470296</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6728902</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>73919894</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dalarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>470196</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6728915</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30176-2024 artfynd.xlsx
+++ b/artfynd/A 30176-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919878</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919882</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919871</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919880</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919896</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919870</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919879</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919895</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919874</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919876</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919877</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919872</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919873</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919881</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919893</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,8 +2309,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919894</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>